--- a/WorkBot/main/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260529.xlsx
+++ b/WorkBot/main/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Triphammer_20260529.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,6 +626,153 @@
         <v>46.28</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>41787</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cont Anchor - 12oz (microwavable)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>97.18000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>97.18000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15509</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.29</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22435</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Container - Deli (16oz)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>35130</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Foil Roll - 18"</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>27.46</v>
+      </c>
+      <c r="E16" t="n">
+        <v>27.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14909</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lid - Deli (6/32oz)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="E17" t="n">
+        <v>53.62</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lid Anchor - 32oz (Dome) for white</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>41820</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Container - Anchor (32oz)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>51.34</v>
+      </c>
+      <c r="E19" t="n">
+        <v>51.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
